--- a/Spark/Data/Simulated/Bruno/model_run/results/ranking_importancia_VS_cost_Number_SE.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/results/ranking_importancia_VS_cost_Number_SE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -20,19 +20,16 @@
     <t xml:space="preserve">estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">se</t>
+    <t xml:space="preserve">conf.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conf.high</t>
   </si>
   <si>
     <t xml:space="preserve">p.value</t>
   </si>
   <si>
     <t xml:space="preserve">custo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conf.low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conf.high</t>
   </si>
   <si>
     <t xml:space="preserve">sig</t>
@@ -530,848 +527,773 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>-0.32534262249469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.235247157498336</v>
+        <v>-0.78641857865685</v>
       </c>
       <c r="D2" t="n">
+        <v>0.13573333366747</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.166670335486193</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.786427051191428</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.135741806202049</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
         <v>0.887764425361258</v>
       </c>
       <c r="C3" t="n">
-        <v>0.323827898606033</v>
+        <v>0.253073406904145</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00611649711630438</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.253061744093434</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.52246710662908</v>
-      </c>
-      <c r="H3" t="s">
+        <v>1.52245544381837</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00611649711630435</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>-0.231434244260961</v>
       </c>
       <c r="C4" t="n">
-        <v>0.372713560586996</v>
+        <v>-0.961939399561161</v>
       </c>
       <c r="D4" t="n">
+        <v>0.49907091103924</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.534636478210124</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
-        <v>-0.961952823011474</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.499084334489552</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>0.416659306439225</v>
       </c>
       <c r="C5" t="n">
-        <v>0.792119189921184</v>
+        <v>-1.13586577726934</v>
       </c>
       <c r="D5" t="n">
+        <v>1.96918439014779</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.598884161125173</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="n">
-        <v>-1.1358943058063</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.96921291868475</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
       </c>
       <c r="J5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" t="n">
         <v>4.21832050211461</v>
       </c>
       <c r="C6" t="n">
-        <v>0.470096704641261</v>
+        <v>3.29694789176678</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000000000000000000287751307698297</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.29693096101774</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.13971004321148</v>
-      </c>
-      <c r="H6" t="s">
+        <v>5.13969311246245</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
         <v>27</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
       </c>
       <c r="J6" t="s">
         <v>28</v>
       </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="n">
         <v>1.13368830791099</v>
       </c>
       <c r="C7" t="n">
-        <v>0.236347203899063</v>
+        <v>0.670456300422085</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00000161295195080173</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.670447788268829</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.59692882755316</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="b">
+        <v>1.5969203153999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.00000161295195089117</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
       </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>-0.358395856229488</v>
       </c>
       <c r="C8" t="n">
-        <v>0.235157860650337</v>
+        <v>-0.819296793785637</v>
       </c>
       <c r="D8" t="n">
+        <v>0.102505081326661</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.127492483948244</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
         <v>33</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.819305263104149</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.102513550645172</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>0.882389138651673</v>
       </c>
       <c r="C9" t="n">
-        <v>0.323703143014651</v>
+        <v>0.247942636660538</v>
       </c>
       <c r="D9" t="n">
+        <v>1.51683564064281</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.00641223776823496</v>
       </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.247930978342956</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.51684729896039</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
       <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>-0.181709916165963</v>
       </c>
       <c r="C10" t="n">
-        <v>0.372566347709616</v>
+        <v>-0.911926539528437</v>
       </c>
       <c r="D10" t="n">
+        <v>0.548506707196511</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.625744652324961</v>
       </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.91193995767681</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.548520125344884</v>
-      </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>0.822132018421392</v>
       </c>
       <c r="C11" t="n">
-        <v>0.791880510381932</v>
+        <v>-0.729925261986391</v>
       </c>
       <c r="D11" t="n">
+        <v>2.37418929882918</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.299175969551397</v>
       </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.729953781927195</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.37421781876998</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" t="n">
         <v>4.24848128068819</v>
       </c>
       <c r="C12" t="n">
-        <v>0.469998531328782</v>
+        <v>3.32730108649706</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.32728415928378</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.16967840209261</v>
-      </c>
-      <c r="H12" t="s">
+        <v>5.16966147487933</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
         <v>27</v>
       </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
       <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" t="n">
         <v>1.07846773494253</v>
       </c>
       <c r="C13" t="n">
-        <v>0.235824100684795</v>
+        <v>0.616260990913782</v>
       </c>
       <c r="D13" t="n">
+        <v>1.54067447897127</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.0000048036082849201</v>
       </c>
-      <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.61625249760033</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.54068297228473</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="b">
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
       <c r="J13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
         <v>-0.367339072027716</v>
       </c>
       <c r="C14" t="n">
-        <v>0.235042491115762</v>
+        <v>-0.828013889451186</v>
       </c>
       <c r="D14" t="n">
+        <v>0.0933357453957531</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.118084962960594</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.82802235461461</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0933442105591775</v>
-      </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="n">
         <v>0.862883070450078</v>
       </c>
       <c r="C15" t="n">
-        <v>0.323495142880296</v>
+        <v>0.22884424123106</v>
       </c>
       <c r="D15" t="n">
+        <v>1.4969218996691</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.00764461703223573</v>
       </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.228832590404698</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.49693355049546</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
         <v>17</v>
       </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
       <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>-0.134373016582496</v>
       </c>
       <c r="C16" t="n">
-        <v>0.372322623508197</v>
+        <v>-0.864111949288028</v>
       </c>
       <c r="D16" t="n">
+        <v>0.595365916123037</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.718170626034175</v>
       </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.864125358658562</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.595379325493571</v>
-      </c>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="n">
         <v>1.54833369336577</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7908870563761</v>
+        <v>-0.00177645297028017</v>
       </c>
       <c r="D17" t="n">
+        <v>3.09844383970183</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.0502631316404392</v>
       </c>
-      <c r="E17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.0018049371313813</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.09847232386293</v>
-      </c>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="n">
         <v>4.24037392970668</v>
       </c>
       <c r="C18" t="n">
-        <v>0.469749950579859</v>
+        <v>3.31968094483069</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3.31966402657016</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.1610838328432</v>
-      </c>
-      <c r="H18" t="s">
+        <v>5.16106691458267</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
         <v>27</v>
       </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
       <c r="J18" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="n">
         <v>0.956388371857609</v>
       </c>
       <c r="C19" t="n">
-        <v>0.235139727113328</v>
+        <v>0.49552297538091</v>
       </c>
       <c r="D19" t="n">
+        <v>1.41725376833431</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.0000475570411773152</v>
       </c>
-      <c r="E19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.495514506715486</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.41726223699973</v>
-      </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" t="b">
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="b">
         <v>1</v>
       </c>
+      <c r="I19" t="s">
+        <v>30</v>
+      </c>
       <c r="J19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
         <v>-0.388733297388444</v>
       </c>
       <c r="C20" t="n">
-        <v>0.235048881774058</v>
+        <v>-0.849420640272012</v>
       </c>
       <c r="D20" t="n">
+        <v>0.071954045495123</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.098159978906756</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" t="s">
         <v>47</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.849429105665599</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.07196251088871</v>
-      </c>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="n">
         <v>0.855324667140227</v>
       </c>
       <c r="C21" t="n">
-        <v>0.32350661407788</v>
+        <v>0.221263354787084</v>
       </c>
       <c r="D21" t="n">
+        <v>1.48938597949337</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.00819527263751407</v>
       </c>
-      <c r="E21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.221251703547582</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.48939763073287</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
         <v>17</v>
       </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
       <c r="J21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
         <v>-0.00721315363115466</v>
       </c>
       <c r="C22" t="n">
-        <v>0.372354732599156</v>
+        <v>-0.737015018998542</v>
       </c>
       <c r="D22" t="n">
+        <v>0.722588711736233</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.984544566037591</v>
       </c>
-      <c r="E22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.7370284295255</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.722602122263191</v>
-      </c>
-      <c r="H22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>2.53792315742989</v>
       </c>
       <c r="C23" t="n">
-        <v>0.791027841244294</v>
+        <v>0.987537077822603</v>
       </c>
       <c r="D23" t="n">
+        <v>4.08830923703717</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.00133481918684408</v>
       </c>
-      <c r="E23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.987508588591071</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4.0883377262687</v>
-      </c>
-      <c r="H23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" t="b">
+      <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="b">
         <v>1</v>
       </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
       <c r="J23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="n">
         <v>4.17735106935617</v>
       </c>
       <c r="C24" t="n">
-        <v>0.469848366826119</v>
+        <v>3.25646519218202</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3.25644827037698</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5.09825386833537</v>
-      </c>
-      <c r="H24" t="s">
+        <v>5.09823694653033</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
         <v>27</v>
       </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
       <c r="J24" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" t="n">
         <v>0.899121370124216</v>
       </c>
       <c r="C25" t="n">
-        <v>0.235114723955979</v>
+        <v>0.438304978935421</v>
       </c>
       <c r="D25" t="n">
+        <v>1.35993776131301</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.000131207253581067</v>
       </c>
-      <c r="E25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.438296511170497</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.35994622907794</v>
-      </c>
-      <c r="H25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25" t="b">
+      <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" t="b">
         <v>1</v>
       </c>
+      <c r="I25" t="s">
+        <v>30</v>
+      </c>
       <c r="J25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
